--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>В этот ход воспользуйся тремя разными предложениями Маркета</t>
+          <t>В этот ход воспользуйся тремя разными предложениями Рынка</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="N28" s="12" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M29" s="13" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Имей в трофеях жетон врага</t>
+          <t>Имей среди уничтоженных жетонов жетон врага</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Имей в трофеях два жетона</t>
+          <t>Имей среди уничтоженных жетонов два жетона</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Имей в трофеях жетон врага</t>
+          <t>Имей среди уничтоженных жетонов жетон врага</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="N32" s="12" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="N34" s="12" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В МАРКЕТЕ (не карта)</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задания 1.15.0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сколько чего" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Задания 1.15.0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сколько чего" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Задания 1.15.0'!$A$1:$N$41</definedName>
@@ -942,12 +942,12 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: пехота или техника</t>
+          <t>ПЕРЕНОС ОГНЯ: атака по твоему жетону переходит на другой твой жетон в том же гексе; нет другого — возьми 1 боеприпас</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>войска стоят без прикрытия зданий — щит на пехоту и технику ровно про это положение: спасти жетон или додержать карту</t>
+          <t>войска стоят без прикрытия: перенос огня даёт выбрать, кто примет удар — это положение: спасти жетон или додержать карту</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: пехота или вышка-здания</t>
+          <t>РАСЧЁТ БАТАРЕИ: когда по твоей вышке нанесён урон, она немедленно делает одну атаку</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>карта про вышки, и щит закрывает вышку — но сжёг щит, и вторую вышку уже не додержать</t>
+          <t>вышка неподвижна и потому обречена принимать удар: утиль даёт ей ответить — но сжёг карту, и вторую вышку уже не додержать</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: техника или вышка-здания</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: чужое войско, вставшее на гекс рядом с твоим военным зданием, получает 1 урон</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>войско в военном здании — это техника и вышка; щит на них и стоит</t>
+          <t>здание с гарнизоном стоит у врага: заградительный огонь бьёт того, кто подошёл</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Имей своё войско на гексе, где есть войска врага</t>
+          <t>Имей своё войско на гексе, где есть здания врага</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: пехота или авиация</t>
+          <t>ОКОП: до конца чужого действия каждая атака по твоим жетонам в одном выбранном гексе стоит атакующему на 1 боеприпас дороже</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>стоять на чужом гексе значит получить удар первым: щит спасает — но тогда карта не сыграна</t>
+          <t>войско стоит у врага под окнами, и бить будут именно там: окоп делает эти удары дороже — больше не заходят, а на гекс с чужими зданиями — заходят. И стоит там дорого: гекс закрыт чужим зданием, значит бить в нём можно только по зданиям и вышкам</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: техника или авиация</t>
+          <t>ОТХОД: перемести один свой жетон из атакуемого гекса на один гекс; уже разыгранные атаки остаются</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>вывести весь вид на поле — значит подставить его; щит на технику и авиацию бережёт именно то, чего в запасе уже нет</t>
+          <t>вывел весь род на поле — значит подставил его целиком; отход уводит жетон из-под серии, но карта в этот ход уже не сыграна</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: авиация или вышка-здания</t>
+          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>трофеи берут в бою, а щит бой переживает: карта одной темы, но половины исключают друг друга</t>
+          <t>низ копит СВОИ трофеи, утиль отнимает ЧУЖОЙ: одна тема, разные стороны стола — и обе половины одновременно не сыграть</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: пехота или техника</t>
+          <t>ПЕРЕНОС ОГНЯ: атака по твоему жетону переходит на другой твой жетон в том же гексе; нет другого — возьми 1 боеприпас</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -2875,7 +2875,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: техника или авиация</t>
+          <t>РАСЧЁТ БАТАРЕИ: когда по твоей вышке нанесён урон, она немедленно делает одну атаку</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -2895,7 +2895,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: пехота или авиация</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: чужое войско, вставшее на гекс рядом с твоим военным зданием, получает 1 урон</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
@@ -2915,7 +2915,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: авиация или вышка-здания</t>
+          <t>ОКОП: до конца чужого действия каждая атака по твоим жетонам в одном выбранном гексе стоит атакующему на 1 боеприпас дороже</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -2935,7 +2935,7 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: пехота или вышка-здания</t>
+          <t>ОТХОД: перемести один свой жетон из атакуемого гекса на один гекс; уже разыгранные атаки остаются</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -2955,7 +2955,7 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>в действие бой - ЩИТ: техника или вышка-здания</t>
+          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -942,12 +942,12 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>ПЕРЕНОС ОГНЯ: атака по твоему жетону переходит на другой твой жетон в том же гексе; нет другого — возьми 1 боеприпас</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>войска стоят без прикрытия: перенос огня даёт выбрать, кто примет удар — это положение: спасти жетон или додержать карту</t>
+          <t>войска стоят без прикрытия и получат первыми — зато огрызнутся бесплатно; это положение: спасти жетон или додержать карту</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>РАСЧЁТ БАТАРЕИ: когда по твоей вышке нанесён урон, она немедленно делает одну атаку</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>вышка неподвижна и потому обречена принимать удар: утиль даёт ей ответить — но сжёг карту, и вторую вышку уже не додержать</t>
+          <t>вышка неподвижна и обречена принимать удар: прочность 2 значит она уцелеет и ответит — но сжёг карту, и вторую вышку уже не додержать</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: чужое войско, вставшее на гекс рядом с твоим военным зданием, получает 1 урон</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>здание с гарнизоном стоит у врага: заградительный огонь бьёт того, кто подошёл</t>
+          <t>гарнизон выходит из-под снесённого здания живым — и сразу отвечает тому, кто снёс</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>ОКОП: до конца чужого действия каждая атака по твоим жетонам в одном выбранном гексе стоит атакующему на 1 боеприпас дороже</t>
+          <t>РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>войско стоит у врага под окнами, и бить будут именно там: окоп делает эти удары дороже — больше не заходят, а на гекс с чужими зданиями — заходят. И стоит там дорого: гекс закрыт чужим зданием, значит бить в нём можно только по зданиям и вышкам</t>
+          <t>войско стоит у врага под окнами, в чужой застройке и среди чужих жетонов — больше не заходят, а на гекс с чужими зданиями — заходят. И стоит там дорого: гекс закрыт чужим зданием, значит бить в нём можно только по зданиям и вышкам</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>ОТХОД: перемести один свой жетон из атакуемого гекса на один гекс; уже разыгранные атаки остаются</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>вывел весь род на поле — значит подставил его целиком; отход уводит жетон из-под серии, но карта в этот ход уже не сыграна</t>
+          <t>вывел весь род на поле — значит подставил его целиком; зато каждый уцелевший огрызается, и добивать приходится с первого удара</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2855,7 +2855,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -2865,17 +2865,17 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>ПЕРЕНОС ОГНЯ: атака по твоему жетону переходит на другой твой жетон в том же гексе; нет другого — возьми 1 боеприпас</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>РАСЧЁТ БАТАРЕИ: когда по твоей вышке нанесён урон, она немедленно делает одну атаку</t>
+          <t>РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -2895,7 +2895,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: чужое войско, вставшее на гекс рядом с твоим военным зданием, получает 1 урон</t>
+          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
@@ -2915,7 +2915,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>ОКОП: до конца чужого действия каждая атака по твоим жетонам в одном выбранном гексе стоит атакующему на 1 боеприпас дороже</t>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -2945,67 +2945,67 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>ОТХОД: перемести один свой жетон из атакуемого гекса на один гекс; уже разыгранные атаки остаются</t>
+          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ</t>
+          <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ</t>
+          <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ</t>
+          <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
@@ -3015,7 +3015,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -3045,194 +3045,134 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t>СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>6</v>
-      </c>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>6</v>
-      </c>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>семейство</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>карт</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>средняя цена</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>2</v>
-      </c>
+          <t>Выработка</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Засада</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>семейство</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>карт</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>средняя цена</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Обеспечение</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Выработка</t>
+          <t>Развертывание</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="D17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Засада</t>
+          <t>Расплата</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="17" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="D18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Обеспечение</t>
+          <t>Устранение</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>4.22</v>
+        <v>3.38</v>
       </c>
       <c r="D19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Развертывание</t>
+          <t>Экспансия</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="D20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Расплата</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="D21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Устранение</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="D22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Экспансия</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="D23" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -659,17 +659,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>добыче перемещение войск не нужно вовсе — верх открывает другую дверь, а не ту же самую</t>
+          <t>карта про два запитанных добытчика — а добытчик №3 и №4 прочностью 2 уцелеет под первым ударом и огрызнётся: низ выставляет мишени, верх учит их кусаться</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>верх подвозит войска к чужому тайлу, низ требует опустошить свой: одно вместо другого</t>
+          <t>низ гонит добытчик к чужому зарождению, верх уводит жетон из-под удара: обе половины про выход из-под чужого хода, но сыграть можно одну</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>гарнизон выходит из-под снесённого здания живым — и сразу отвечает тому, кто снёс</t>
+          <t>вся карта про здание, за которым прячется войско: заградительный огонь даёт этому зданию огрызнуться — но сжёг верх, и держать позицию нечем</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>сбросу арсенала перемещение не нужно; и наоборот — сжёг верх, и сбрасывать уже незачем</t>
+          <t>низ платит картой арсенала, верх — тем, что карта уходит в костёр: обе половины про расставание с картой, и обе одновременно не сыграть</t>
         </is>
       </c>
     </row>
@@ -1867,17 +1867,17 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>маневр боеприпасов не тратит, поэтому не мешает низу — но и не помогает ему: выбор чистый</t>
+          <t>низ требует отдать боеприпасы, отход их не тратит вовсе — потому и уместен: остаться без патронов и всё-таки уйти из-под удара</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>два трофея — дело времени; маневр подводит войска, но сам трофея не приносит</t>
+          <t>низ копит чужие обломки, верх защищает свои здания: одна война, но разные её концы</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё войско, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -2875,7 +2875,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ОТХОД: в чужое действие Бой перемести один свой жетон из атакуемого гекса на один гекс. Уже разыгранные атаки остаются</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
+          <t>РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -2945,57 +2945,57 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>МАНЕВР ДВУМЯ ВОЙСКАМИ</t>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
+          <t>СМЕНА ЭНЕРГИИ ИЛИ СМЕНА МОДУЛЕЙ</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
@@ -3035,144 +3035,164 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>СПЕЦ ДЕЙСТВИЕ</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>1 ОБМЕН В НАУКЕ (не трек) / 1 ОБМЕН В РЫНКЕ (не карта)</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>СНЯТЬ ВЕСЬ УРОН СО ВСЕХ жетонов на гексе</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D12" s="17" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-    </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>семейство</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>карт</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>средняя цена</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Выработка</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="D14" s="17" t="inlineStr"/>
+      <c r="D14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Засада</t>
+          <t>Выработка</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>3.79</v>
+        <v>3.29</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Обеспечение</t>
+          <t>Засада</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>4.22</v>
+        <v>3.79</v>
       </c>
       <c r="D16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Развертывание</t>
+          <t>Обеспечение</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>3.48</v>
+        <v>4.22</v>
       </c>
       <c r="D17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Расплата</t>
+          <t>Развертывание</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C18" s="17" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="D18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Устранение</t>
+          <t>Расплата</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="D19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
+          <t>Устранение</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="D20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
           <t>Экспансия</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B21" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C21" s="17" t="n">
         <v>3.62</v>
       </c>
-      <c r="D20" s="17" t="inlineStr"/>
+      <c r="D21" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -664,12 +664,12 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>карта про два запитанных добытчика — а добытчик №3 и №4 прочностью 2 уцелеет под первым ударом и огрызнётся: низ выставляет мишени, верх учит их кусаться</t>
+          <t>низ выставляет два добытчика на виду, верх учит их огрызаться — даже тот, что гибнет от первого же удара, успевает выстрелить в убийцу</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>РАЗЫГРАЙ БОЙ ПЕРЕД ЧУЖИМ БОЕМ</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: твоё ЗДАНИЕ, получившее урон и уцелевшее, немедленно наносит 1 урон одному жетону напавшего в своём или соседнем гексе — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -664,12 +664,12 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>низ выставляет два добытчика на виду, верх учит их огрызаться — даже тот, что гибнет от первого же удара, успевает выстрелить в убийцу</t>
+          <t>низ выставляет два добытчика на виду, верх делает их снос платным: добытчик с прочностью 1 гибнет от первого удара — и ранит того, кто его снёс</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>войска стоят без прикрытия и получат первыми — зато огрызнутся бесплатно; это положение: спасти жетон или додержать карту</t>
+          <t>войска стоят без прикрытия и умрут первыми — зато не даром: каждое забирает с собой рану. Но сжёг верх — и держать двоих уже нечем</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>вышка неподвижна и обречена принимать удар: прочность 2 значит она уцелеет и ответит — но сжёг карту, и вторую вышку уже не додержать</t>
+          <t>вышка неподвижна и рано или поздно её снесут: пусть снос обойдётся сносящему в рану — но сжёг карту, и вторую вышку уже не додержать</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>вся карта про здание, за которым прячется войско: заградительный огонь даёт этому зданию огрызнуться — но сжёг верх, и держать позицию нечем</t>
+          <t>вся карта про здание, за которым прячется войско: снесли укрытие — здание успевает выстрелить, а гарнизон выходит живым. Но сжёг верх, и держать позицию нечем</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>вывел весь род на поле — значит подставил его целиком; зато каждый уцелевший огрызается, и добивать приходится с первого удара</t>
+          <t>вывел весь род на поле — значит подставил его целиком; зато каждый убитый жетон достаётся врагу с раной в придачу</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>ОТВЕТНЫЙ ОГОНЬ: твоё ВОЙСКО, получившее урон и уцелевшее, немедленно делает одну атаку по жетонам напавшего — НЕ платя боеприпасов. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ОТВЕТНЫЙ ОГОНЬ: в чужой бой — если твоё ВОЙСКО уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: когда твоё ЗДАНИЕ получает урон — даже если этим ударом оно уничтожено — немедленно нанеси 1 урон жетону, который его атаковал. Один раз за чужой ход; ответных атак не вызывает</t>
+          <t>ЗАГРАДИТЕЛЬНЫЙ ОГОНЬ: в чужой бой — если твоё ЗДАНИЕ уничтожают, оно наносит 1 урон жетону, который его уничтожил</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -2470,12 +2470,12 @@
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
-          <t>цена 4.1 — верх обязан быть слабым, иначе карту всегда сожгут; боеприпас при этом пригодится тому самому бою</t>
+          <t>низ забирает чужой жетон себе в трофеи, верх не даёт забрать твой: одна и та же война с двух сторон стола, и обе половины сразу не сыграть</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>РИКОШЕТ: атака, назначенная по твоему жетону, переходит на любой другой жетон в том же гексе — чей угодно и любого типа. Жетон внутри здания целью не становится</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
         <is>
-          <t>занимать гексы — дело маневра, и маневра здесь нарочно НЕТ: он закрывал бы низ сам. Остаётся скромный боеприпас</t>
+          <t>низ раскидывает войска по чужим гексам, а рикошет тем и живёт, что на гексе тесно от чужих жетонов: положение одно, а пользы от него две</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Научного Отдела</t>
+          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Научного Отдела</t>
+          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов два жетона</t>
+          <t>Имей среди уничтоженных жетонов два жетона врага</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -2774,7 +2774,7 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>На 3 из них есть жетоны противника</t>
+          <t>На 2 из них есть здания противника</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
-          <t>то же и здесь: пять гексов при цене 4.1 обязаны выигрывать у костра</t>
+          <t>растянулся по полю и стоишь в чужой застройке — верх даёт ударить первым, пока не ударили по тебе; но сжёг его, и пять гексов держать нечем</t>
         </is>
       </c>
     </row>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1359,14 +1359,14 @@
       </c>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="6" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>самая дорогая карта колоды — и самый скромный утиль на ней</t>
+          <t>пара к карте 13: то же требование, та же цена, но платят разным — там карты заданий, здесь монеты с боеприпасом. Утиль скромный у обеих</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="D17" s="17" t="inlineStr"/>
     </row>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1305,12 +1305,14 @@
       <c r="G14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -1329,7 +1331,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>слабый верх при цене 4.2: выполнение должно выигрывать; обмен в науке здесь не дан нарочно — он закрывал бы низ сам</t>
+          <t>слабый верх при цене 3.85: выполнение должно выигрывать; обмен в науке здесь не дан нарочно — он закрывал бы низ сам</t>
         </is>
       </c>
     </row>
@@ -1359,14 +1361,12 @@
       </c>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="6" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>пара к карте 13: то же требование, та же цена, но платят разным — там карты заданий, здесь монеты с боеприпасом. Утиль скромный у обеих</t>
+          <t>пара к карте 13: то же требование и почти та же цена, но платят разным — там смесь с картой задания, здесь чистые монеты</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>4.16</v>
+        <v>4.01</v>
       </c>
       <c r="D17" s="17" t="inlineStr"/>
     </row>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -811,12 +811,12 @@
       <c r="G5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1193,14 +1193,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -1303,16 +1303,14 @@
       </c>
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -1360,13 +1358,13 @@
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="n">
-        <v>4</v>
-      </c>
+      <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="J15" s="6" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -1961,12 +1959,12 @@
       </c>
       <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="10" t="inlineStr"/>
       <c r="J26" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
@@ -2015,12 +2013,12 @@
       </c>
       <c r="F27" s="12" t="inlineStr"/>
       <c r="G27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="12" t="inlineStr"/>
       <c r="I27" s="12" t="inlineStr"/>
       <c r="J27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -2069,12 +2067,12 @@
       </c>
       <c r="F28" s="12" t="inlineStr"/>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="12" t="inlineStr"/>
       <c r="I28" s="12" t="inlineStr"/>
       <c r="J28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -2123,12 +2121,12 @@
       </c>
       <c r="F29" s="12" t="inlineStr"/>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="12" t="inlineStr"/>
       <c r="I29" s="12" t="inlineStr"/>
       <c r="J29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -2177,12 +2175,12 @@
       </c>
       <c r="F30" s="12" t="inlineStr"/>
       <c r="G30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="12" t="inlineStr"/>
       <c r="I30" s="12" t="inlineStr"/>
       <c r="J30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -2231,12 +2229,12 @@
       </c>
       <c r="F31" s="12" t="inlineStr"/>
       <c r="G31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="12" t="inlineStr"/>
       <c r="I31" s="12" t="inlineStr"/>
       <c r="J31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -2285,12 +2283,12 @@
       </c>
       <c r="F32" s="12" t="inlineStr"/>
       <c r="G32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32" s="12" t="inlineStr"/>
       <c r="I32" s="12" t="inlineStr"/>
       <c r="J32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -2725,12 +2723,12 @@
       </c>
       <c r="F40" s="14" t="inlineStr"/>
       <c r="G40" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" s="14" t="inlineStr"/>
       <c r="I40" s="14" t="inlineStr"/>
       <c r="J40" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
@@ -3106,7 +3104,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="D15" s="17" t="inlineStr"/>
     </row>
@@ -3134,7 +3132,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="D17" s="17" t="inlineStr"/>
     </row>
@@ -3162,7 +3160,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="D19" s="17" t="inlineStr"/>
     </row>
@@ -3176,7 +3174,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="D20" s="17" t="inlineStr"/>
     </row>
@@ -3190,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="D21" s="17" t="inlineStr"/>
     </row>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>обмен на планшете не производит боеприпасы приказом, поэтому низ он не закрывает — но выручает, когда производить нечем</t>
+          <t>боеприпасов на планшете рынка больше нет вовсе (02.09.2026), так что обмен низ не закрывает даже отдалённо: он про келемий и трофеи, а низ про производство приказом</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>дорогое задание — верх обязан быть скромным, иначе костёр всегда выгоднее; и обмена на планшете здесь нет нарочно, иначе вышел бы автомат</t>
+          <t>после снятия боеприпасов и ячейки энергии на планшете осталось ДВА печатных обмена, значит три предложения набираются ровно впритык: два печатных плюс одно с карты. Верх обязан быть скромным</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>слабый верх при цене 3.85: выполнение должно выигрывать; обмен в науке здесь не дан нарочно — он закрывал бы низ сам</t>
+          <t>на планшете науки три обмена (02.09.2026), значит три предложения — это ровно все они за один ход. Обмен в верх не дан нарочно: он закрывал бы низ сам</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>В МОМЕНТЕ</t>
+          <t>СПЕЦ ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
+          <t>АТАКА ОДНИМ ВОЙСКОМ</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>СПЕЦ ДЕЙСТВИЕ</t>
+          <t>В МОМЕНТЕ</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>АТАКА ОДНИМ ВОЙСКОМ</t>
+          <t>плюс 1 боеприпас в приказ ОПЕРАЦИЯ</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>контейнеры сдаются закрытыми, атака к ним не относится: два разных способа распорядиться картой</t>
+          <t>контейнеры сдаются закрытыми, и боеприпас им ничем не поможет: самый скромный верх достаётся заданию, которое платят чужой валютой</t>
         </is>
       </c>
     </row>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Задания 1.15.0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Сколько чего" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задания 1.15.0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сколько чего" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Задания 1.15.0'!$A$1:$N$41</definedName>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N30" s="12" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>низ копит чужие обломки, верх защищает свои здания: одна война, но разные её концы</t>
+          <t>низ копит чужие трофеи, верх защищает свои здания: одна война, но разные её концы</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N35" s="12" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1565,12 +1565,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД перенеси два своих здания на другие гексы</t>
+          <t>В ЭТОТ ХОД снеси своё здание и построй другое</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Одно из перенесённых - твоё ЦУ</t>
+          <t>Построенное встало на тот же гекс, где стояло снесённое</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>переносу зданий атака не нужна; зато она нужна тому, кому переносить уже нечего</t>
+          <t>перестройке атака не нужна; зато она нужна тому, кому перестраивать уже нечего</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N30" s="12" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>низ копит чужие обломки, верх защищает свои здания: одна война, но разные её концы</t>
+          <t>низ копит чужие трофеи, верх защищает свои здания: одна война, но разные её концы</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N35" s="12" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1349,12 +1349,12 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
+          <t>В ЭТОТ ХОД сдай трофеи на ДВУХ разных треках технологий</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>На трёх треках</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>пара к карте 13: то же требование и почти та же цена, но платят разным — там смесь с картой задания, здесь чистые монеты</t>
+          <t>два трека за ход — это два шага, оплаченных трофеями; атака сверху их не заменит — но пригодится тому, кому сдавать нечего</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй или перенеси своё ЦУ так, чтобы от него до гекса с ЦУ противника осталось не больше 2 гексов</t>
+          <t>В ЭТОТ ХОД поставь своё ЦУ так, чтобы от него до гекса с ЦУ противника осталось не больше 2 гексов</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>перенос ЦУ — это стройка, а не смена энергии: верх не подменяет низ, но выручает, когда ЦУ уехало и всё осталось без питания</t>
+          <t>постановка ЦУ — это стройка, а не смена энергии: верх не подменяет низ, но выручает, когда ЦУ уехало и всё осталось без питания</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетон врага</t>
+          <t>Имей среди уничтоженных жетонов жетоны ДВУХ разных противников</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>два жетона, оба ценностью 2 и выше</t>
+          <t>И оба этих жетона — здания</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr"/>

--- a/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — карты целиком.xlsx
@@ -1398,17 +1398,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД</t>
+          <t>СОСТОЯНИЕ</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД поставь своё ЦУ так, чтобы от него до гекса с ЦУ противника осталось не больше 2 гексов</t>
+          <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД поставь его так, чтобы оно примыкало к зданию противника</t>
+          <t>Твоих зданий вокруг чужого ЦУ два, и стоят они на разных гексах</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>постановка ЦУ — это стройка, а не смена энергии: верх не подменяет низ, но выручает, когда ЦУ уехало и всё осталось без питания</t>
+          <t>подобраться зданием к чужому штабу — это стройка, а смена энергии её не заменит; зато выручит того, у кого стройка уже встала без питания</t>
         </is>
       </c>
     </row>
